--- a/artfynd/A 50156-2024 artfynd.xlsx
+++ b/artfynd/A 50156-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121149617</v>
       </c>
       <c r="B2" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149612</v>
+        <v>121149614</v>
       </c>
       <c r="B3" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739357</v>
+        <v>739127</v>
       </c>
       <c r="R3" t="n">
-        <v>7291496</v>
+        <v>7291436</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -900,7 +900,7 @@
         <v>121149616</v>
       </c>
       <c r="B4" t="n">
-        <v>89743</v>
+        <v>89753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149614</v>
+        <v>121149612</v>
       </c>
       <c r="B5" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739127</v>
+        <v>739357</v>
       </c>
       <c r="R5" t="n">
-        <v>7291436</v>
+        <v>7291496</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 50156-2024 artfynd.xlsx
+++ b/artfynd/A 50156-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149617</v>
+        <v>121149616</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>89753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739637</v>
+        <v>739299</v>
       </c>
       <c r="R2" t="n">
-        <v>7291216</v>
+        <v>7291450</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149616</v>
+        <v>121149612</v>
       </c>
       <c r="B4" t="n">
-        <v>89753</v>
+        <v>78337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739299</v>
+        <v>739357</v>
       </c>
       <c r="R4" t="n">
-        <v>7291450</v>
+        <v>7291496</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149612</v>
+        <v>121149617</v>
       </c>
       <c r="B5" t="n">
-        <v>78337</v>
+        <v>91973</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739357</v>
+        <v>739637</v>
       </c>
       <c r="R5" t="n">
-        <v>7291496</v>
+        <v>7291216</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 50156-2024 artfynd.xlsx
+++ b/artfynd/A 50156-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149616</v>
+        <v>121149612</v>
       </c>
       <c r="B2" t="n">
-        <v>89753</v>
+        <v>78340</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739299</v>
+        <v>739357</v>
       </c>
       <c r="R2" t="n">
-        <v>7291450</v>
+        <v>7291496</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149614</v>
+        <v>121149617</v>
       </c>
       <c r="B3" t="n">
-        <v>78337</v>
+        <v>91985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739127</v>
+        <v>739637</v>
       </c>
       <c r="R3" t="n">
-        <v>7291436</v>
+        <v>7291216</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149612</v>
+        <v>121149616</v>
       </c>
       <c r="B4" t="n">
-        <v>78337</v>
+        <v>89760</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739357</v>
+        <v>739299</v>
       </c>
       <c r="R4" t="n">
-        <v>7291496</v>
+        <v>7291450</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149617</v>
+        <v>121149614</v>
       </c>
       <c r="B5" t="n">
-        <v>91973</v>
+        <v>78340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739637</v>
+        <v>739127</v>
       </c>
       <c r="R5" t="n">
-        <v>7291216</v>
+        <v>7291436</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 50156-2024 artfynd.xlsx
+++ b/artfynd/A 50156-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149612</v>
+        <v>121149616</v>
       </c>
       <c r="B2" t="n">
-        <v>78340</v>
+        <v>89761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739357</v>
+        <v>739299</v>
       </c>
       <c r="R2" t="n">
-        <v>7291496</v>
+        <v>7291450</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149617</v>
+        <v>121149612</v>
       </c>
       <c r="B3" t="n">
-        <v>91985</v>
+        <v>78340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739637</v>
+        <v>739357</v>
       </c>
       <c r="R3" t="n">
-        <v>7291216</v>
+        <v>7291496</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149616</v>
+        <v>121149614</v>
       </c>
       <c r="B4" t="n">
-        <v>89760</v>
+        <v>78340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739299</v>
+        <v>739127</v>
       </c>
       <c r="R4" t="n">
-        <v>7291450</v>
+        <v>7291436</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149614</v>
+        <v>121149617</v>
       </c>
       <c r="B5" t="n">
-        <v>78340</v>
+        <v>91986</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739127</v>
+        <v>739637</v>
       </c>
       <c r="R5" t="n">
-        <v>7291436</v>
+        <v>7291216</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 50156-2024 artfynd.xlsx
+++ b/artfynd/A 50156-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149616</v>
+        <v>121149612</v>
       </c>
       <c r="B2" t="n">
-        <v>89761</v>
+        <v>78343</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739299</v>
+        <v>739357</v>
       </c>
       <c r="R2" t="n">
-        <v>7291450</v>
+        <v>7291496</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149612</v>
+        <v>121149616</v>
       </c>
       <c r="B3" t="n">
-        <v>78340</v>
+        <v>89764</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739357</v>
+        <v>739299</v>
       </c>
       <c r="R3" t="n">
-        <v>7291496</v>
+        <v>7291450</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149614</v>
+        <v>121149617</v>
       </c>
       <c r="B4" t="n">
-        <v>78340</v>
+        <v>91989</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739127</v>
+        <v>739637</v>
       </c>
       <c r="R4" t="n">
-        <v>7291436</v>
+        <v>7291216</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149617</v>
+        <v>121149614</v>
       </c>
       <c r="B5" t="n">
-        <v>91986</v>
+        <v>78343</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739637</v>
+        <v>739127</v>
       </c>
       <c r="R5" t="n">
-        <v>7291216</v>
+        <v>7291436</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 50156-2024 artfynd.xlsx
+++ b/artfynd/A 50156-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149612</v>
+        <v>121149614</v>
       </c>
       <c r="B2" t="n">
         <v>78343</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739357</v>
+        <v>739127</v>
       </c>
       <c r="R2" t="n">
-        <v>7291496</v>
+        <v>7291436</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149616</v>
+        <v>121149612</v>
       </c>
       <c r="B3" t="n">
-        <v>89764</v>
+        <v>78343</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739299</v>
+        <v>739357</v>
       </c>
       <c r="R3" t="n">
-        <v>7291450</v>
+        <v>7291496</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149614</v>
+        <v>121149616</v>
       </c>
       <c r="B5" t="n">
-        <v>78343</v>
+        <v>89764</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739127</v>
+        <v>739299</v>
       </c>
       <c r="R5" t="n">
-        <v>7291436</v>
+        <v>7291450</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 50156-2024 artfynd.xlsx
+++ b/artfynd/A 50156-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149614</v>
+        <v>121149616</v>
       </c>
       <c r="B2" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739127</v>
+        <v>739299</v>
       </c>
       <c r="R2" t="n">
-        <v>7291436</v>
+        <v>7291450</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149612</v>
+        <v>121149617</v>
       </c>
       <c r="B3" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739357</v>
+        <v>739637</v>
       </c>
       <c r="R3" t="n">
-        <v>7291496</v>
+        <v>7291216</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149617</v>
+        <v>121149612</v>
       </c>
       <c r="B4" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739637</v>
+        <v>739357</v>
       </c>
       <c r="R4" t="n">
-        <v>7291216</v>
+        <v>7291496</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149616</v>
+        <v>121149614</v>
       </c>
       <c r="B5" t="n">
-        <v>89764</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739299</v>
+        <v>739127</v>
       </c>
       <c r="R5" t="n">
-        <v>7291450</v>
+        <v>7291436</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 50156-2024 artfynd.xlsx
+++ b/artfynd/A 50156-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149616</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149617</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149612</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149614</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>